--- a/fine_tuning_excel_pack_brand_voice/03_test_prompts_after_finetune_UTF8_FIXED.xlsx
+++ b/fine_tuning_excel_pack_brand_voice/03_test_prompts_after_finetune_UTF8_FIXED.xlsx
@@ -8,19 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\baitap\NT114\NT114-Git\NT114.Q21-Web-Copy-Writing\fine_tuning_excel_pack_brand_voice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79B2B39F-A7AE-406C-9BAE-F4A98737ED88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFBC1540-4488-475E-ADC1-B12665DC68A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2244" yWindow="2052" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2244" yWindow="2052" windowWidth="17280" windowHeight="8880" xr2:uid="{8E087B83-AE5B-4970-BBF2-1EC4B990498C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Prompts" sheetId="1" r:id="rId1"/>
+    <sheet name="TestPrompts" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="58">
   <si>
     <t>prompt</t>
   </si>
@@ -28,12 +47,24 @@
     <t>expected_focus</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
+    <t>type</t>
+  </si>
+  <si>
+    <t>tone</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>audience</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
+Sản phẩm/dịch vụ: áo khoác chống nắng nhẹ.
+Từ khóa chính: vải thoáng; có mũ; dễ gấp gọn.
+Đối tượng mục tiêu: người đi làm di chuyển ban ngày.
+Thông tin bổ sung: ưu đãi freeship hôm nay.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -51,38 +82,27 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Keep Vietnamese diacritics, follow Generator UI format, return exactly 3 separate versions, and avoid invented claims.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Headline: một câu chính sắc, dễ đọc, có lợi ích hoặc điểm khác biệt.
-Subheadline: một câu phụ làm rõ lời hứa của headline.
-Lời kêu gọi hành động: một câu ngắn thúc đẩy người đọc hành động.
-Không viết thành email, social post, mô tả sản phẩm hoặc landing page đầy đủ.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
+    <t>Giữ tiếng Việt có dấu; prompt và output theo Generator UI; đúng 3 phiên bản; đúng label theo loại nội dung; không bịa chứng nhận hay số liệu.</t>
+  </si>
+  <si>
+    <t>headline</t>
+  </si>
+  <si>
+    <t>friendly</t>
+  </si>
+  <si>
+    <t>áo khoác chống nắng nhẹ</t>
+  </si>
+  <si>
+    <t>người đi làm di chuyển ban ngày</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
+Sản phẩm/dịch vụ: áo khoác chống nắng nhẹ.
+Từ khóa chính: vải thoáng; có mũ; dễ gấp gọn.
+Đối tượng mục tiêu: người đi làm di chuyển ban ngày.
+Thông tin bổ sung: ưu đãi freeship hôm nay.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -101,36 +121,18 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Mô tả ngắn: đoạn mở đầu giới thiệu sản phẩm/dịch vụ.
-Lợi ích chính: 2-3 bullet.
-Đặc điểm nổi bật: 2-3 bullet.
-Lời kêu gọi hành động: lời kêu gọi mua, đăng ký hoặc liên hệ.
-Không dùng format email, SEO metadata hoặc caption mạng xã hội.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Social Media Post với tone Thân thiện.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
+    <t>description</t>
+  </si>
+  <si>
+    <t>professional</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Social Media Post với tone Khẩn cấp.
+Sản phẩm/dịch vụ: áo khoác chống nắng nhẹ.
+Từ khóa chính: vải thoáng; có mũ; dễ gấp gọn.
+Đối tượng mục tiêu: người đi làm di chuyển ban ngày.
+Thông tin bổ sung: ưu đãi freeship hôm nay.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -149,36 +151,18 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Social Media Post với tone Khẩn cấp.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Hook: câu mở đầu kéo chú ý.
-Caption: nội dung chính dễ đọc trên mạng xã hội.
-Lời kêu gọi hành động: hành động mong muốn.
-Hashtags: 3-6 hashtag liên quan.
-Không thêm Subject, Preview text, SEO title hoặc Meta description.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Email Marketing với tone Chuyên nghiệp.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
+    <t>social</t>
+  </si>
+  <si>
+    <t>urgent</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Email Marketing với tone Cảm xúc.
+Sản phẩm/dịch vụ: áo khoác chống nắng nhẹ.
+Từ khóa chính: vải thoáng; có mũ; dễ gấp gọn.
+Đối tượng mục tiêu: người đi làm di chuyển ban ngày.
+Thông tin bổ sung: ưu đãi freeship hôm nay.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -198,12 +182,18 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>emotional</t>
+  </si>
+  <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
-Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
-Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
-Đối tượng mục tiêu: dân văn phòng mang cà phê đi làm.
-Thông tin bổ sung: freeship cho đơn từ 2 sản phẩm.
+Sản phẩm/dịch vụ: áo khoác chống nắng nhẹ.
+Từ khóa chính: vải thoáng; có mũ; dễ gấp gọn.
+Đối tượng mục tiêu: người đi làm di chuyển ban ngày.
+Thông tin bổ sung: ưu đãi freeship hôm nay.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -220,12 +210,15 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
+    <t>cta</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Tiêu Đề Quảng Cáo với tone Chuyên nghiệp.
+Sản phẩm/dịch vụ: bàn phím cơ yên tĩnh.
+Từ khóa chính: switch êm; layout gọn; đèn nền dịu.
+Đối tượng mục tiêu: người làm việc trong văn phòng chung.
+Thông tin bổ sung: bảo hành 12 tháng.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -243,35 +236,18 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Headline: một câu chính sắc, dễ đọc, có lợi ích hoặc điểm khác biệt.
-Subheadline: một câu phụ làm rõ lời hứa của headline.
-Lời kêu gọi hành động: một câu ngắn thúc đẩy người đọc hành động.
-Không viết thành email, social post, mô tả sản phẩm hoặc landing page đầy đủ.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
+    <t>bàn phím cơ yên tĩnh</t>
+  </si>
+  <si>
+    <t>người làm việc trong văn phòng chung</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Mô Tả Sản Phẩm với tone Khẩn cấp.
+Sản phẩm/dịch vụ: bàn phím cơ yên tĩnh.
+Từ khóa chính: switch êm; layout gọn; đèn nền dịu.
+Đối tượng mục tiêu: người làm việc trong văn phòng chung.
+Thông tin bổ sung: bảo hành 12 tháng.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -291,35 +267,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Mô tả ngắn: đoạn mở đầu giới thiệu sản phẩm/dịch vụ.
-Lợi ích chính: 2-3 bullet.
-Đặc điểm nổi bật: 2-3 bullet.
-Lời kêu gọi hành động: lời kêu gọi mua, đăng ký hoặc liên hệ.
-Không dùng format email, SEO metadata hoặc caption mạng xã hội.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Social Media Post với tone Thân thiện.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
+Hãy viết Social Media Post với tone Cảm xúc.
+Sản phẩm/dịch vụ: bàn phím cơ yên tĩnh.
+Từ khóa chính: switch êm; layout gọn; đèn nền dịu.
+Đối tượng mục tiêu: người làm việc trong văn phòng chung.
+Thông tin bổ sung: bảo hành 12 tháng.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -339,35 +291,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Social Media Post với tone Khẩn cấp.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Hook: câu mở đầu kéo chú ý.
-Caption: nội dung chính dễ đọc trên mạng xã hội.
-Lời kêu gọi hành động: hành động mong muốn.
-Hashtags: 3-6 hashtag liên quan.
-Không thêm Subject, Preview text, SEO title hoặc Meta description.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Email Marketing với tone Chuyên nghiệp.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
+Hãy viết Email Marketing với tone Thân thiện.
+Sản phẩm/dịch vụ: bàn phím cơ yên tĩnh.
+Từ khóa chính: switch êm; layout gọn; đèn nền dịu.
+Đối tượng mục tiêu: người làm việc trong văn phòng chung.
+Thông tin bổ sung: bảo hành 12 tháng.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -388,11 +316,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
-Sản phẩm/dịch vụ: đèn bàn LED chống chói.
-Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
-Đối tượng mục tiêu: sinh viên học khuya và làm việc tại nhà.
-Thông tin bổ sung: giảm 10 phần trăm cho khách mới.
+Hãy viết Lời Kêu Gọi Hành Động với tone Chuyên nghiệp.
+Sản phẩm/dịch vụ: bàn phím cơ yên tĩnh.
+Từ khóa chính: switch êm; layout gọn; đèn nền dịu.
+Đối tượng mục tiêu: người làm việc trong văn phòng chung.
+Thông tin bổ sung: bảo hành 12 tháng.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -411,10 +339,10 @@
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
+Sản phẩm/dịch vụ: sữa hạt ít đường.
+Từ khóa chính: ít đường; vị dễ uống; đóng chai tiện.
+Đối tượng mục tiêu: người muốn bữa sáng nhanh gọn.
+Thông tin bổ sung: mua combo tiết kiệm hơn.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -432,35 +360,18 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Headline: một câu chính sắc, dễ đọc, có lợi ích hoặc điểm khác biệt.
-Subheadline: một câu phụ làm rõ lời hứa của headline.
-Lời kêu gọi hành động: một câu ngắn thúc đẩy người đọc hành động.
-Không viết thành email, social post, mô tả sản phẩm hoặc landing page đầy đủ.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
+    <t>sữa hạt ít đường</t>
+  </si>
+  <si>
+    <t>người muốn bữa sáng nhanh gọn</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
+Sản phẩm/dịch vụ: sữa hạt ít đường.
+Từ khóa chính: ít đường; vị dễ uống; đóng chai tiện.
+Đối tượng mục tiêu: người muốn bữa sáng nhanh gọn.
+Thông tin bổ sung: mua combo tiết kiệm hơn.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -480,35 +391,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Mô tả ngắn: đoạn mở đầu giới thiệu sản phẩm/dịch vụ.
-Lợi ích chính: 2-3 bullet.
-Đặc điểm nổi bật: 2-3 bullet.
-Lời kêu gọi hành động: lời kêu gọi mua, đăng ký hoặc liên hệ.
-Không dùng format email, SEO metadata hoặc caption mạng xã hội.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
+Sản phẩm/dịch vụ: sữa hạt ít đường.
+Từ khóa chính: ít đường; vị dễ uống; đóng chai tiện.
+Đối tượng mục tiêu: người muốn bữa sáng nhanh gọn.
+Thông tin bổ sung: mua combo tiết kiệm hơn.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -528,35 +415,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Social Media Post với tone Khẩn cấp.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Hook: câu mở đầu kéo chú ý.
-Caption: nội dung chính dễ đọc trên mạng xã hội.
-Lời kêu gọi hành động: hành động mong muốn.
-Hashtags: 3-6 hashtag liên quan.
-Không thêm Subject, Preview text, SEO title hoặc Meta description.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
+Sản phẩm/dịch vụ: sữa hạt ít đường.
+Từ khóa chính: ít đường; vị dễ uống; đóng chai tiện.
+Đối tượng mục tiêu: người muốn bữa sáng nhanh gọn.
+Thông tin bổ sung: mua combo tiết kiệm hơn.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -577,11 +440,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
-Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
-Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
-Đối tượng mục tiêu: người mới bắt đầu skincare.
-Thông tin bổ sung: tặng túi du lịch mini.
+Hãy viết Lời Kêu Gọi Hành Động với tone Khẩn cấp.
+Sản phẩm/dịch vụ: sữa hạt ít đường.
+Từ khóa chính: ít đường; vị dễ uống; đóng chai tiện.
+Đối tượng mục tiêu: người muốn bữa sáng nhanh gọn.
+Thông tin bổ sung: mua combo tiết kiệm hơn.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -599,11 +462,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
-Sản phẩm/dịch vụ: máy xay sinh tố mini.
-Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
-Đối tượng mục tiêu: người bận rộn muốn chuẩn bị đồ uống nhanh.
-Thông tin bổ sung: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Hãy viết Tiêu Đề Quảng Cáo với tone Cảm xúc.
+Sản phẩm/dịch vụ: camera trong nhà.
+Từ khóa chính: góc rộng; đàm thoại hai chiều; cảnh báo chuyển động.
+Đối tượng mục tiêu: gia đình muốn quan sát thú cưng.
+Thông tin bổ sung: hỗ trợ cài đặt từ xa.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -621,35 +484,18 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
-Sản phẩm/dịch vụ: máy xay sinh tố mini.
-Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
-Đối tượng mục tiêu: người bận rộn muốn chuẩn bị đồ uống nhanh.
-Thông tin bổ sung: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
-Độ dài mong muốn: vừa đủ chi tiết.
-Giới hạn output tối đa: 1800 tokens.
-Tạo đúng 3 phiên bản riêng biệt.
-Định dạng bắt buộc:
-Phiên bản 1: ...
-Phiên bản 2: ...
-Phiên bản 3: ...
-Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
-Format riêng theo loại nội dung:
-Headline: một câu chính sắc, dễ đọc, có lợi ích hoặc điểm khác biệt.
-Subheadline: một câu phụ làm rõ lời hứa của headline.
-Lời kêu gọi hành động: một câu ngắn thúc đẩy người đọc hành động.
-Không viết thành email, social post, mô tả sản phẩm hoặc landing page đầy đủ.
-Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
-Temperature tham khảo: 0.7.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
-Sản phẩm/dịch vụ: máy xay sinh tố mini.
-Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
-Đối tượng mục tiêu: người bận rộn muốn chuẩn bị đồ uống nhanh.
-Thông tin bổ sung: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+    <t>camera trong nhà</t>
+  </si>
+  <si>
+    <t>gia đình muốn quan sát thú cưng</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Mô Tả Sản Phẩm với tone Thân thiện.
+Sản phẩm/dịch vụ: camera trong nhà.
+Từ khóa chính: góc rộng; đàm thoại hai chiều; cảnh báo chuyển động.
+Đối tượng mục tiêu: gia đình muốn quan sát thú cưng.
+Thông tin bổ sung: hỗ trợ cài đặt từ xa.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -669,11 +515,111 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Social Media Post với tone Chuyên nghiệp.
+Sản phẩm/dịch vụ: camera trong nhà.
+Từ khóa chính: góc rộng; đàm thoại hai chiều; cảnh báo chuyển động.
+Đối tượng mục tiêu: gia đình muốn quan sát thú cưng.
+Thông tin bổ sung: hỗ trợ cài đặt từ xa.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Hook: câu mở đầu kéo chú ý.
+Caption: nội dung chính dễ đọc trên mạng xã hội.
+Lời kêu gọi hành động: hành động mong muốn.
+Hashtags: 3-6 hashtag liên quan.
+Không thêm Subject, Preview text, SEO title hoặc Meta description.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Email Marketing với tone Khẩn cấp.
+Sản phẩm/dịch vụ: camera trong nhà.
+Từ khóa chính: góc rộng; đàm thoại hai chiều; cảnh báo chuyển động.
+Đối tượng mục tiêu: gia đình muốn quan sát thú cưng.
+Thông tin bổ sung: hỗ trợ cài đặt từ xa.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Subject: dòng tiêu đề email.
+Preview text: đoạn xem trước ngắn.
+Lời chào: lời chào phù hợp người nhận.
+Nội dung chính: tách thành các đoạn ngắn, có thể có bullet nếu cần.
+Lời kêu gọi hành động: hành động chính trong email.
+Không viết như social caption, landing page hoặc SEO snippet.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Lời Kêu Gọi Hành Động với tone Cảm xúc.
+Sản phẩm/dịch vụ: camera trong nhà.
+Từ khóa chính: góc rộng; đàm thoại hai chiều; cảnh báo chuyển động.
+Đối tượng mục tiêu: gia đình muốn quan sát thú cưng.
+Thông tin bổ sung: hỗ trợ cài đặt từ xa.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Lời kêu gọi hành động chính: câu/nút kêu gọi hành động.
+Microcopy: một câu hỗ trợ ngay dưới lời kêu gọi hành động.
+Chỉ viết lời kêu gọi hành động, không thêm bài quảng cáo dài.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
+Sản phẩm/dịch vụ: giày chạy bộ êm chân.
+Từ khóa chính: đế êm; thoáng khí; ôm chân vừa phải.
+Đối tượng mục tiêu: người mới tập chạy.
+Thông tin bổ sung: đổi size miễn phí một lần.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Headline: một câu chính sắc, dễ đọc, có lợi ích hoặc điểm khác biệt.
+Subheadline: một câu phụ làm rõ lời hứa của headline.
+Lời kêu gọi hành động: một câu ngắn thúc đẩy người đọc hành động.
+Không viết thành email, social post, mô tả sản phẩm hoặc landing page đầy đủ.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>giày chạy bộ êm chân</t>
+  </si>
+  <si>
+    <t>người mới tập chạy</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
-Sản phẩm/dịch vụ: máy xay sinh tố mini.
-Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
-Đối tượng mục tiêu: người bận rộn muốn chuẩn bị đồ uống nhanh.
-Thông tin bổ sung: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Sản phẩm/dịch vụ: giày chạy bộ êm chân.
+Từ khóa chính: đế êm; thoáng khí; ôm chân vừa phải.
+Đối tượng mục tiêu: người mới tập chạy.
+Thông tin bổ sung: đổi size miễn phí một lần.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -693,11 +639,11 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Social Media Post với tone Thân thiện.
-Sản phẩm/dịch vụ: máy xay sinh tố mini.
-Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
-Đối tượng mục tiêu: người bận rộn muốn chuẩn bị đồ uống nhanh.
-Thông tin bổ sung: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Hãy viết Social Media Post với tone Khẩn cấp.
+Sản phẩm/dịch vụ: giày chạy bộ êm chân.
+Từ khóa chính: đế êm; thoáng khí; ôm chân vừa phải.
+Đối tượng mục tiêu: người mới tập chạy.
+Thông tin bổ sung: đổi size miễn phí một lần.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -717,11 +663,111 @@
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
-Hãy viết Social Media Post với tone Khẩn cấp.
-Sản phẩm/dịch vụ: máy xay sinh tố mini.
-Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
-Đối tượng mục tiêu: người bận rộn muốn chuẩn bị đồ uống nhanh.
-Thông tin bổ sung: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Hãy viết Email Marketing với tone Cảm xúc.
+Sản phẩm/dịch vụ: giày chạy bộ êm chân.
+Từ khóa chính: đế êm; thoáng khí; ôm chân vừa phải.
+Đối tượng mục tiêu: người mới tập chạy.
+Thông tin bổ sung: đổi size miễn phí một lần.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Subject: dòng tiêu đề email.
+Preview text: đoạn xem trước ngắn.
+Lời chào: lời chào phù hợp người nhận.
+Nội dung chính: tách thành các đoạn ngắn, có thể có bullet nếu cần.
+Lời kêu gọi hành động: hành động chính trong email.
+Không viết như social caption, landing page hoặc SEO snippet.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
+Sản phẩm/dịch vụ: giày chạy bộ êm chân.
+Từ khóa chính: đế êm; thoáng khí; ôm chân vừa phải.
+Đối tượng mục tiêu: người mới tập chạy.
+Thông tin bổ sung: đổi size miễn phí một lần.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Lời kêu gọi hành động chính: câu/nút kêu gọi hành động.
+Microcopy: một câu hỗ trợ ngay dưới lời kêu gọi hành động.
+Chỉ viết lời kêu gọi hành động, không thêm bài quảng cáo dài.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Tiêu Đề Quảng Cáo với tone Chuyên nghiệp.
+Sản phẩm/dịch vụ: hộp cơm giữ nhiệt.
+Từ khóa chính: giữ ấm lâu; nhiều ngăn; dễ rửa.
+Đối tượng mục tiêu: nhân viên văn phòng mang cơm trưa.
+Thông tin bổ sung: tặng túi giữ nhiệt.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Headline: một câu chính sắc, dễ đọc, có lợi ích hoặc điểm khác biệt.
+Subheadline: một câu phụ làm rõ lời hứa của headline.
+Lời kêu gọi hành động: một câu ngắn thúc đẩy người đọc hành động.
+Không viết thành email, social post, mô tả sản phẩm hoặc landing page đầy đủ.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>hộp cơm giữ nhiệt</t>
+  </si>
+  <si>
+    <t>nhân viên văn phòng mang cơm trưa</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Mô Tả Sản Phẩm với tone Khẩn cấp.
+Sản phẩm/dịch vụ: hộp cơm giữ nhiệt.
+Từ khóa chính: giữ ấm lâu; nhiều ngăn; dễ rửa.
+Đối tượng mục tiêu: nhân viên văn phòng mang cơm trưa.
+Thông tin bổ sung: tặng túi giữ nhiệt.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Mô tả ngắn: đoạn mở đầu giới thiệu sản phẩm/dịch vụ.
+Lợi ích chính: 2-3 bullet.
+Đặc điểm nổi bật: 2-3 bullet.
+Lời kêu gọi hành động: lời kêu gọi mua, đăng ký hoặc liên hệ.
+Không dùng format email, SEO metadata hoặc caption mạng xã hội.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Social Media Post với tone Cảm xúc.
+Sản phẩm/dịch vụ: hộp cơm giữ nhiệt.
+Từ khóa chính: giữ ấm lâu; nhiều ngăn; dễ rửa.
+Đối tượng mục tiêu: nhân viên văn phòng mang cơm trưa.
+Thông tin bổ sung: tặng túi giữ nhiệt.
 Độ dài mong muốn: vừa đủ chi tiết.
 Giới hạn output tối đa: 1800 tokens.
 Tạo đúng 3 phiên bản riêng biệt.
@@ -739,28 +785,100 @@
 Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
 Temperature tham khảo: 0.7.</t>
   </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Email Marketing với tone Thân thiện.
+Sản phẩm/dịch vụ: hộp cơm giữ nhiệt.
+Từ khóa chính: giữ ấm lâu; nhiều ngăn; dễ rửa.
+Đối tượng mục tiêu: nhân viên văn phòng mang cơm trưa.
+Thông tin bổ sung: tặng túi giữ nhiệt.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Subject: dòng tiêu đề email.
+Preview text: đoạn xem trước ngắn.
+Lời chào: lời chào phù hợp người nhận.
+Nội dung chính: tách thành các đoạn ngắn, có thể có bullet nếu cần.
+Lời kêu gọi hành động: hành động chính trong email.
+Không viết như social caption, landing page hoặc SEO snippet.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
+  <si>
+    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Hãy viết Lời Kêu Gọi Hành Động với tone Chuyên nghiệp.
+Sản phẩm/dịch vụ: hộp cơm giữ nhiệt.
+Từ khóa chính: giữ ấm lâu; nhiều ngăn; dễ rửa.
+Đối tượng mục tiêu: nhân viên văn phòng mang cơm trưa.
+Thông tin bổ sung: tặng túi giữ nhiệt.
+Độ dài mong muốn: vừa đủ chi tiết.
+Giới hạn output tối đa: 1800 tokens.
+Tạo đúng 3 phiên bản riêng biệt.
+Định dạng bắt buộc:
+Phiên bản 1: ...
+Phiên bản 2: ...
+Phiên bản 3: ...
+Mỗi phiên bản phải tự đứng độc lập, không gom chung thành một đoạn lớn.
+Format riêng theo loại nội dung:
+Lời kêu gọi hành động chính: câu/nút kêu gọi hành động.
+Microcopy: một câu hỗ trợ ngay dưới lời kêu gọi hành động.
+Chỉ viết lời kêu gọi hành động, không thêm bài quảng cáo dài.
+Dùng tiếng Việt tự nhiên, đầy đủ dấu, có lời kêu gọi hành động rõ ràng.
+Temperature tham khảo: 0.7.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -775,14 +893,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1116,264 +1235,638 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529EB6C6-FBE4-42CB-A3BF-F4971C1E5928}">
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="90" customWidth="1"/>
-    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="1" max="1" width="72.77734375" customWidth="1"/>
+    <col min="2" max="2" width="62.77734375" customWidth="1"/>
+    <col min="3" max="4" width="14.77734375" customWidth="1"/>
+    <col min="5" max="5" width="24.77734375" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>3</v>
+    </row>
+    <row r="13" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>